--- a/data/output/evaluasi_12.xlsx
+++ b/data/output/evaluasi_12.xlsx
@@ -7,14 +7,40 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="1225" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="1278" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="1204" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="1200" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="1221" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="1202" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="1208" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="1222" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="1272" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="1203" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="1209" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="1209" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="1222" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="1273" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="1207" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="1210" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="1213" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="1214" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="1217" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="1218" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="1219" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="1223" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="1224" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="1225" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="1271" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="1272" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="1274" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="1275" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="1277" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="1205" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="1201" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="1206" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="1212" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="1204" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="1216" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="1211" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="1215" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="1220" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet name="1203" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet name="1276" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet name="1278" sheetId="34" state="visible" r:id="rId34"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -432,6 +458,834 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>provinsi</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Sumatera Utara</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-15.90170712058658</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q1-25 vs q-to-q_pkp_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>12</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Sumatera Utara</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>7.497982382015748</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q2-25 vs q-to-q_pkp_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>12</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Sumatera Utara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.5661488239562197</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25 vs q-to-q_pkp_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Sumatera Utara</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.06090864755882681</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25 vs y-on-y_pklnprt_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>12</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Sumatera Utara</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>2.157781343263137</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q1-25 vs y-on-y_pkp_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>12</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Sumatera Utara</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.1564163294428956</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25 vs y-on-y_pkp_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>12</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Sumatera Utara</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>2.295199578408901</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q1-25 vs y-on-y_pmtb_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>12</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Sumatera Utara</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>2.157781343263137</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q1-25 vs c-to-c_pkp_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Sumatera Utara</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>2.295199578408901</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q1-25 vs c-to-c_pmtb_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>12</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Sumatera Utara</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0.818952508482976</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q3-25 vs implisit_q-to-q_pklnprt_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1213</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Langkat</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-3.917785290141571</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q1-25_ril vs sog_y-on-y_pi_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1214</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Nias Selatan</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-2.931604510034434</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q1-25_ril vs sog_y-on-y_pi_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1214</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Nias Selatan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0.7758189215194141</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q3-25_prov vs q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1214</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Nias Selatan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-5.040731501523799</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1214</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Nias Selatan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.1258568414993993</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q3-25_prov vs implisit_q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1217</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Samosir</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-6.244051138580719</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q1-25_ril vs sog_y-on-y_pi_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1217</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Samosir</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-5.663681559283291</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q2-25_ril vs sog_y-on-y_pi_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1217</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Samosir</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-1.930680588308674</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1217</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Samosir</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>4.728806697592645</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1217</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Samosir</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>6.992399726610728</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1217</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Samosir</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>3.644188860721654</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1217</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Samosir</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>5.362291608209543</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1217</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Samosir</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-5.935249733042719</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -469,6 +1323,806 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
+        <v>1218</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Serdang Bedagai</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-2.954200986903233</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q1-25_ril vs sog_y-on-y_pi_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1218</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Serdang Bedagai</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0.1646472919378458</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q3-25_prov vs q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1218</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Serdang Bedagai</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>1.275199530810817</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1219</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Batu Bara</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-4.437372655201305</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q1-25_ril vs sog_y-on-y_pi_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1219</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Batu Bara</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0.3177097968793227</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q3-25_prov vs q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1219</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Batu Bara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.1705736822171041</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1219</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Batu Bara</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>2.711278486260404</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1219</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Batu Bara</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-2.154605303782546</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1219</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Batu Bara</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.8860355070279096</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1223</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Labuhan Batu Utara</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-3.905826313261938</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q1-25_ril vs sog_y-on-y_pi_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1223</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Labuhan Batu Utara</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0.005763602269467887</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q3-25_prov vs q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1223</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Labuhan Batu Utara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>1.053102638920055</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1223</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Labuhan Batu Utara</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0.9006298657893012</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1223</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Labuhan Batu Utara</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.3808707011079552</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1223</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Labuhan Batu Utara</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-2.20170436670056</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1224</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Nias Utara</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-4.689602587801612</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q1-25_ril vs sog_y-on-y_pi_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1224</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Nias Utara</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-2.857190281323299</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q2-25_ril vs sog_y-on-y_pi_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1224</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Nias Utara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.3025553158933983</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q3-25_prov vs q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1224</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Nias Utara</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>2.155117834831392</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1224</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Nias Utara</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>4.890464961394924</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1224</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Nias Utara</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>4.551469131627847</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1224</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Nias Utara</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-2.986924248973501</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
         <v>1225</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -482,16 +2136,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-304.82</v>
+        <v>-9.409753089069154</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>adhb_pi_q1-25_ril vs adhb_pi_q1-25_rev</t>
+          <t>sog_y-on-y_pi_q1-25_ril vs sog_y-on-y_pi_q1-25_rev</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
@@ -506,20 +2160,20 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-612.50693324</v>
+        <v>-3.829797483564085</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>adhk_pi_q1-25_ril vs adhk_pi_q1-25_rev</t>
+          <t>sog_y-on-y_pi_q2-25_ril vs sog_y-on-y_pi_q2-25_rev</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
@@ -534,20 +2188,560 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.3820336097601834</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q3-25_prov vs q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1225</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Nias Barat</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1.151756701331989</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1225</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Nias Barat</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1.950832717699717</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1225</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Nias Barat</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>4.771909155777379</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1225</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Nias Barat</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-1.064883867923349</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1225</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Nias Barat</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-4.932180415323705</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1225</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Nias Barat</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-4.070652505784254</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1225</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Nias Barat</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-4.237481549227979</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1271</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kota Sibolga</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>q1-25</t>
         </is>
       </c>
+      <c r="D2" t="n">
+        <v>-2.45715656738798</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q1-25_ril vs sog_y-on-y_pi_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1271</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kota Sibolga</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.11605182329611</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1271</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kota Sibolga</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
       <c r="D4" t="n">
-        <v>0.1506748224247571</v>
+        <v>3.398363271739872</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>sog_q_pi_q1-25_ril vs sog_q_pi_q1-25_rev</t>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1272</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kota Tanjung Balai</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-2.884481119316147</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q1-25_ril vs sog_y-on-y_pi_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1272</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kota Tanjung Balai</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-2.565598040069501</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q2-25_ril vs sog_y-on-y_pi_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1272</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kota Tanjung Balai</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>3.468237612748513</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1272</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kota Tanjung Balai</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>3.243409233665691</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1272</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kota Tanjung Balai</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-4.670246050203867</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1272</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kota Tanjung Balai</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-2.529834788269516</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
@@ -562,7 +2756,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -599,57 +2793,1917 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1278</v>
+        <v>1221</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kota Gunungsitoli</t>
+          <t>Kabupaten Padang Lawas</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-2430.3954364037</v>
+        <v>23.113233318049</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>adhb_pi_q1-25_ril vs adhb_pi_q1-25_rev</t>
+          <t>adhb_pi_q2-25_ril vs adhb_pi_q2-25_rev</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>Nilai revisi lebih dari (+-30%) dari nilai rilis</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1278</v>
+        <v>1221</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kota Gunungsitoli</t>
+          <t>Kabupaten Padang Lawas</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>12.864201513936</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>adhk_pi_q2-25_ril vs adhk_pi_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Nilai revisi lebih dari (+-30%) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1221</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Padang Lawas</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.001603531280376723</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q2-25_ril vs sog_q_pi_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1221</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Padang Lawas</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>9.52371026676529</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1221</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Padang Lawas</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.4750681858376559</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1221</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Padang Lawas</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-5.820949189612038</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1221</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Padang Lawas</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>7.496596772703434</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q3-25_prov vs implisit_y-on-y_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1274</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kota Tebing Tinggi</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>q1-25</t>
         </is>
       </c>
+      <c r="D2" t="n">
+        <v>-5.157441710159937</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q1-25_ril vs sog_y-on-y_pi_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1274</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kota Tebing Tinggi</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
       <c r="D3" t="n">
-        <v>0.8144574454986336</v>
+        <v>-2.460404163450608</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pklnprt_q1-25_ril vs implisit_q-to-q_pklnprt_q1-25_rev</t>
+          <t>sog_y-on-y_pi_q2-25_ril vs sog_y-on-y_pi_q2-25_rev</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1274</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kota Tebing Tinggi</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.3481017740520375</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1274</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kota Tebing Tinggi</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>2.903094781067823</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1274</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kota Tebing Tinggi</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.3501364446038817</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1274</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kota Tebing Tinggi</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-2.343137141092698</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1275</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kota Medan</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-2.222143911794886</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q1-25_ril vs sog_y-on-y_pi_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1275</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kota Medan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>5.487948816556483</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1275</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kota Medan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.6716334121491834</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1275</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kota Medan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-6.13979663301179</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1277</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kota Padang Sidempuan</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-2.005128084689098</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q1-25_ril vs sog_y-on-y_pi_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1277</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kota Padang Sidempuan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>1.002389703731295</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q3-25_prov vs q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1277</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kota Padang Sidempuan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.9111764004047564</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1277</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kota Padang Sidempuan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1.099320617159382</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1205</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Tapanuli Utara</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.5992766956673673</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1205</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Tapanuli Utara</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-1.06085144938582</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1205</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Tapanuli Utara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.03973337596659698</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q3-25_prov vs c-to-c_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1201</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Nias</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>1.544558767289631</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q3-25_prov vs q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1201</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Nias</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0.4636829748956597</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1201</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Nias</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>11.72942566346566</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1201</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Nias</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0.7556747938082387</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1201</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Nias</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-2.869876545446472</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1201</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Nias</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1.861775891777821</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1201</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Nias</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-3.962020174085638</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1201</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Nias</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-2.083963676309229</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q3-25_prov vs implisit_q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1206</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Toba</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.8856451117957829</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q3-25_prov vs q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1206</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Toba</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>2.94816184025017</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1206</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Toba</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.08739962869264935</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1206</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Toba</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.5693442525628225</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1206</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Toba</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>2.442164551461377</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1212</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Deli Serdang</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.07224758738307352</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q3-25_prov vs q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1212</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Deli Serdang</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-6.304795119802904</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1212</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Deli Serdang</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>1.619206717617151</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1204</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Tapanuli Tengah</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>1.787518766402252</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1204</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Tapanuli Tengah</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>4.215383293598857</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1204</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Tapanuli Tengah</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>9.86391415954559</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1204</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Tapanuli Tengah</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>5.716252194598305</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q3-25_prov vs c-to-c_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1204</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Tapanuli Tengah</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.8812248405940875</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1216</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Pakpak Bharat</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.1273315821918596</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1216</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Pakpak Bharat</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>9.329435327143713</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1216</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Pakpak Bharat</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>8.850856134756805</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1216</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Pakpak Bharat</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-1.775014851106785</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q3-25_prov vs implisit_q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1211</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Karo</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>1.259951020016169</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1211</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Karo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-15.80929479164955</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1211</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Karo</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-8.840050852756846</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -664,6 +4718,462 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1202</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Mandailing Natal</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>984.357518045</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>adhk_pi_q2-25_ril vs adhk_pi_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Nilai revisi lebih dari (+-30%) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1202</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Mandailing Natal</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-3.35914698685119</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q1-25_ril vs sog_y-on-y_pi_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1202</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Mandailing Natal</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-9.787504993164706</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1202</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Mandailing Natal</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-15.98729957911782</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1202</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Mandailing Natal</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-2.670002303095107</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1202</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Mandailing Natal</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-12.68429174604979</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1202</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Mandailing Natal</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-3.215299115432219</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1202</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Mandailing Natal</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>7.950311993727952</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q3-25_prov vs implisit_y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1202</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Mandailing Natal</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-2.065258561361385</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1215</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Humbang Hasundutan</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>1.59852058959268</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1215</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Humbang Hasundutan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-1.983102570096317</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1215</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Humbang Hasundutan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-1.120667557045303</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1215</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Humbang Hasundutan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0.8608532173849683</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -701,57 +5211,307 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1204</v>
+        <v>1220</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Tapanuli Tengah</t>
+          <t>Kabupaten Padang Lawas Utara</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>98272.58985064004</v>
+        <v>-0.3181391049941714</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>adhb_net_ekspor_q1-25_ril vs adhb_net_ekspor_q1-25_rev</t>
+          <t>c-to-c_pklnprt_q3-25_prov vs c-to-c_pklnprt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1204</v>
+        <v>1220</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kabupaten Tapanuli Tengah</t>
+          <t>Kabupaten Padang Lawas Utara</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-2.470619932299424</v>
+        <v>0.6567067016853099</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pmtb_q1-25_ril vs implisit_q-to-q_pmtb_q1-25_rev</t>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1203</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Tapanuli Selatan</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>2.607714363130425</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1276</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kota Binjai</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>2.695657470203945</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1276</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kota Binjai</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.03848165101058657</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q3-25_prov vs implisit_q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1278</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kota Gunungsitoli</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.8462012581847044</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q3-25_prov vs implisit_q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -766,7 +5526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -812,20 +5572,20 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-85179.131809115</v>
+        <v>2.48855335887889</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>adhk_pi_q1-25_ril vs adhk_pi_q1-25_rev</t>
+          <t>sog_q_pi_q2-25_ril vs sog_q_pi_q2-25_rev</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
@@ -844,16 +5604,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4.188837017796957</v>
+        <v>-2.65520784141357</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>y-on-y_pmtb_q1-25_ril vs y-on-y_pmtb_q1-25_rev</t>
+          <t>sog_y-on-y_pi_q1-25_ril vs sog_y-on-y_pi_q1-25_rev</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
@@ -868,20 +5628,20 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>4.188837017796957</v>
+        <v>-8.529999999999974</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>c-to-c_pmtb_q1-25_ril vs c-to-c_pmtb_q1-25_rev</t>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -896,20 +5656,20 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.9421801071631095</v>
+        <v>0.6994963311518323</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pmtb_q1-25_ril vs implisit_q-to-q_pmtb_q1-25_rev</t>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -924,20 +5684,20 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.6222178281131356</v>
+        <v>-2.91546762875018</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>implisit_y-on-y_pmtb_q1-25_ril vs implisit_y-on-y_pmtb_q1-25_rev</t>
+          <t>c-to-c_pklnprt_q3-25_prov vs c-to-c_pklnprt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -952,48 +5712,20 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-1.009011172838224</v>
+        <v>2.496864716457427</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>sog_q_pi_q1-25_ril vs sog_q_pi_q1-25_rev</t>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>1208</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Kabupaten Asahan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>1.049588714107936</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>sog_y-on-y_pmtb_q1-25_ril vs sog_y-on-y_pmtb_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1008,7 +5740,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1045,29 +5777,85 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1222</v>
+        <v>1209</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Labuhan Batu Selatan</t>
+          <t>Kabupaten Simalungun</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>2.241287307503633</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q2-25_ril vs sog_q_pi_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1209</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Simalungun</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>q1-25</t>
         </is>
       </c>
-      <c r="D2" t="n">
-        <v>-30108.072309138</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>adhk_pi_q1-25_ril vs adhk_pi_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+      <c r="D3" t="n">
+        <v>-2.058120084304539</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q1-25_ril vs sog_y-on-y_pi_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1209</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Simalungun</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>1.891950097750667</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1082,7 +5870,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1119,39 +5907,39 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1272</v>
+        <v>1222</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kota Tanjung Balai</t>
+          <t>Kabupaten Labuhan Batu Selatan</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.2430343464051331</v>
+        <v>3.082947636819801</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pkp_q1-25_ril vs implisit_q-to-q_pkp_q1-25_rev</t>
+          <t>sog_q_pi_q2-25_ril vs sog_q_pi_q2-25_rev</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1272</v>
+        <v>1222</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kota Tanjung Balai</t>
+          <t>Kabupaten Labuhan Batu Selatan</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1160,72 +5948,128 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.750193357795631</v>
+        <v>-6.466887243703169</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pmtb_q1-25_ril vs implisit_q-to-q_pmtb_q1-25_rev</t>
+          <t>sog_y-on-y_pi_q1-25_ril vs sog_y-on-y_pi_q1-25_rev</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1272</v>
+        <v>1222</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kota Tanjung Balai</t>
+          <t>Kabupaten Labuhan Batu Selatan</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.8560763096167699</v>
+        <v>-2.749074375542847</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>implisit_y-on-y_pkp_q1-25_ril vs implisit_y-on-y_pkp_q1-25_rev</t>
+          <t>sog_y-on-y_pi_q2-25_ril vs sog_y-on-y_pi_q2-25_rev</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1272</v>
+        <v>1222</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kota Tanjung Balai</t>
+          <t>Kabupaten Labuhan Batu Selatan</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1.884060149826212</v>
+        <v>0.3198974204448571</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>implisit_y-on-y_pmtb_q1-25_ril vs implisit_y-on-y_pmtb_q1-25_rev</t>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1222</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Labuhan Batu Selatan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>3.860050047404849</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1222</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Labuhan Batu Selatan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-2.575878736274908</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
@@ -1240,7 +6084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1277,29 +6121,169 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1203</v>
+        <v>1273</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Tapanuli Selatan</t>
+          <t>Kota Pematang Siantar</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>2.199856389238227</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q2-25_ril vs sog_q_pi_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1273</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kota Pematang Siantar</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>q1-25</t>
         </is>
       </c>
-      <c r="D2" t="n">
-        <v>0.9456148673188154</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>implisit_q-to-q_pmtb_q1-25_ril vs implisit_q-to-q_pmtb_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+      <c r="D3" t="n">
+        <v>-6.403738834815768</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q1-25_ril vs sog_y-on-y_pi_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1273</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kota Pematang Siantar</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-3.768162841150708</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q2-25_ril vs sog_y-on-y_pi_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1273</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kota Pematang Siantar</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.4595154217921677</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q3-25_prov vs c-to-c_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1273</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kota Pematang Siantar</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>2.283871406000431</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1273</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kota Pematang Siantar</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-3.879244142364882</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
@@ -1314,7 +6298,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1351,11 +6335,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1209</v>
+        <v>1207</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Simalungun</t>
+          <t>Kabupaten Labuhan Batu</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1364,16 +6348,258 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.7321542901111585</v>
+        <v>-5.201028993498963</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pmtb_q1-25_ril vs implisit_q-to-q_pmtb_q1-25_rev</t>
+          <t>sog_y-on-y_pi_q1-25_ril vs sog_y-on-y_pi_q1-25_rev</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1207</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Labuhan Batu</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-2.992854784948195</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q2-25_ril vs sog_y-on-y_pi_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1207</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Labuhan Batu</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>1.074982578940962</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1207</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Labuhan Batu</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-2.825908046767448</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1210</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Dairi</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-2.656617800226239</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q1-25_ril vs sog_y-on-y_pi_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1210</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Dairi</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-2.524565548381628</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q2-25_ril vs sog_y-on-y_pi_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1210</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Dairi</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.3820761167053898</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q3-25_prov vs c-to-c_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1210</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Dairi</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-3.028965372521627</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>

--- a/data/output/evaluasi_12.xlsx
+++ b/data/output/evaluasi_12.xlsx
@@ -517,7 +517,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -545,7 +545,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -573,7 +573,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -601,7 +601,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -629,7 +629,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -657,7 +657,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -685,7 +685,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -713,7 +713,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
